--- a/test/fixtures/xlsx/double-star/double-star.xlsx
+++ b/test/fixtures/xlsx/double-star/double-star.xlsx
@@ -12,24 +12,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
-    <t xml:space="preserve">~~table:Doubled~~</t>
+    <t xml:space="preserve">:table Doubled</t>
   </si>
   <si>
     <t xml:space="preserve">Field name carries two index markers.</t>
   </si>
   <si>
-    <t xml:space="preserve">index</t>
+    <t xml:space="preserve">:field</t>
   </si>
   <si>
-    <t xml:space="preserve">primary index</t>
+    <t xml:space="preserve">:type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">index</t>
   </si>
   <si>
     <t xml:space="preserve">int</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">primary index</t>
   </si>
   <si>
     <t xml:space="preserve">cs</t>
@@ -38,10 +47,10 @@
     <t xml:space="preserve">**Code</t>
   </si>
   <si>
-    <t xml:space="preserve">typo for *Code</t>
+    <t xml:space="preserve">string</t>
   </si>
   <si>
-    <t xml:space="preserve">string</t>
+    <t xml:space="preserve">typo for *Code</t>
   </si>
   <si>
     <t xml:space="preserve">Label</t>
@@ -101,44 +110,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:D9"/>
+  <dimension ref="B2:E7"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -146,38 +173,19 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
+      <c r="E7" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
